--- a/data/trans_orig/IP16B98-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16B98-Estudios-trans_orig.xlsx
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21093</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,14%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17006</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32418</t>
+          <t>32484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38513</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13045</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>27078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38830</t>
+          <t>38766</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44216</t>
+          <t>44211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
